--- a/themes_clean.xlsx
+++ b/themes_clean.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E2" t="n">
         <v>11.67000007629395</v>
@@ -499,7 +499,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E3" t="n">
         <v>11.67000007629395</v>
@@ -527,7 +527,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E4" t="n">
         <v>11.67000007629395</v>
@@ -555,7 +555,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E5" t="n">
         <v>11.67000007629395</v>
@@ -583,7 +583,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E6" t="n">
         <v>11.67000007629395</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E7" t="n">
         <v>11.67000007629395</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E8" t="n">
         <v>11.67000007629395</v>
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E9" t="n">
         <v>11.67000007629395</v>
@@ -695,7 +695,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E10" t="n">
         <v>11.67000007629395</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E11" t="n">
         <v>11.67000007629395</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E12" t="n">
         <v>11.67000007629395</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E13" t="n">
         <v>11.67000007629395</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E14" t="n">
         <v>11.67000007629395</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E15" t="n">
         <v>11.67000007629395</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E16" t="n">
         <v>11.67000007629395</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E17" t="n">
         <v>11.67000007629395</v>
@@ -919,7 +919,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E18" t="n">
         <v>11.67000007629395</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E19" t="n">
         <v>11.67000007629395</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E20" t="n">
         <v>11.67000007629395</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E21" t="n">
         <v>11.67000007629395</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E22" t="n">
         <v>11.67000007629395</v>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E23" t="n">
         <v>11.67000007629395</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E24" t="n">
         <v>11.67000007629395</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E25" t="n">
         <v>11.67000007629395</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E26" t="n">
         <v>11.67000007629395</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E27" t="n">
         <v>11.67000007629395</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E28" t="n">
         <v>11.67000007629395</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E29" t="n">
         <v>11.67000007629395</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E30" t="n">
         <v>11.67000007629395</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E31" t="n">
         <v>11.67000007629395</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E32" t="n">
         <v>11.67000007629395</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E33" t="n">
         <v>11.67000007629395</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E34" t="n">
         <v>11.67000007629395</v>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E35" t="n">
         <v>11.67000007629395</v>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E36" t="n">
         <v>11.67000007629395</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E37" t="n">
         <v>11.67000007629395</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E38" t="n">
         <v>11.67000007629395</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E39" t="n">
         <v>11.67000007629395</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E40" t="n">
         <v>11.67000007629395</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E41" t="n">
         <v>11.67000007629395</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E42" t="n">
         <v>11.67000007629395</v>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E43" t="n">
         <v>11.67000007629395</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E44" t="n">
         <v>11.67000007629395</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E45" t="n">
         <v>11.67000007629395</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E46" t="n">
         <v>11.67000007629395</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E47" t="n">
         <v>11.67000007629395</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E48" t="n">
         <v>11.67000007629395</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E49" t="n">
         <v>11.67000007629395</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E50" t="n">
         <v>11.67000007629395</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E51" t="n">
         <v>11.67000007629395</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E52" t="n">
         <v>11.67000007629395</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E53" t="n">
         <v>11.67000007629395</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E54" t="n">
         <v>11.67000007629395</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E55" t="n">
         <v>11.67000007629395</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E56" t="n">
         <v>11.67000007629395</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E57" t="n">
         <v>11.67000007629395</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E58" t="n">
         <v>11.67000007629395</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E59" t="n">
         <v>11.67000007629395</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E60" t="n">
         <v>11.67000007629395</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E61" t="n">
         <v>11.67000007629395</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E62" t="n">
         <v>11.67000007629395</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E63" t="n">
         <v>11.67000007629395</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E64" t="n">
         <v>11.67000007629395</v>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E65" t="n">
         <v>11.67000007629395</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E66" t="n">
         <v>11.67000007629395</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E67" t="n">
         <v>11.67000007629395</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E68" t="n">
         <v>11.67000007629395</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E69" t="n">
         <v>11.67000007629395</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E70" t="n">
         <v>11.67000007629395</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E71" t="n">
         <v>11.67000007629395</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E72" t="n">
         <v>11.67000007629395</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E73" t="n">
         <v>11.67000007629395</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E74" t="n">
         <v>11.67000007629395</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E75" t="n">
         <v>11.67000007629395</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E76" t="n">
         <v>11.67000007629395</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E77" t="n">
         <v>11.67000007629395</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E78" t="n">
         <v>11.67000007629395</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E79" t="n">
         <v>11.67000007629395</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E80" t="n">
         <v>11.67000007629395</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E81" t="n">
         <v>11.67000007629395</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E82" t="n">
         <v>11.67000007629395</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E83" t="n">
         <v>11.67000007629395</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E84" t="n">
         <v>11.67000007629395</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E85" t="n">
         <v>11.67000007629395</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E86" t="n">
         <v>11.67000007629395</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E87" t="n">
         <v>11.67000007629395</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E88" t="n">
         <v>11.67000007629395</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E89" t="n">
         <v>11.67000007629395</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E90" t="n">
         <v>11.67000007629395</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E91" t="n">
         <v>11.67000007629395</v>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E92" t="n">
         <v>11.67000007629395</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E93" t="n">
         <v>11.67000007629395</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E94" t="n">
         <v>11.67000007629395</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E95" t="n">
         <v>11.67000007629395</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E96" t="n">
         <v>11.67000007629395</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E97" t="n">
         <v>11.67000007629395</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E98" t="n">
         <v>11.67000007629395</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E99" t="n">
         <v>11.67000007629395</v>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E100" t="n">
         <v>11.67000007629395</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E101" t="n">
         <v>11.67000007629395</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E102" t="n">
         <v>11.67000007629395</v>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E103" t="n">
         <v>11.67000007629395</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E104" t="n">
         <v>11.67000007629395</v>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E105" t="n">
         <v>11.67000007629395</v>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E106" t="n">
         <v>11.67000007629395</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E107" t="n">
         <v>11.67000007629395</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E108" t="n">
         <v>11.67000007629395</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E109" t="n">
         <v>11.67000007629395</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E110" t="n">
         <v>11.67000007629395</v>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E111" t="n">
         <v>11.67000007629395</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E112" t="n">
         <v>11.67000007629395</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E113" t="n">
         <v>11.67000007629395</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E114" t="n">
         <v>11.67000007629395</v>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E115" t="n">
         <v>11.67000007629395</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E116" t="n">
         <v>11.67000007629395</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E117" t="n">
         <v>11.67000007629395</v>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E118" t="n">
         <v>11.67000007629395</v>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E119" t="n">
         <v>11.67000007629395</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E120" t="n">
         <v>11.67000007629395</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E121" t="n">
         <v>11.67000007629395</v>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E122" t="n">
         <v>11.67000007629395</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E123" t="n">
         <v>11.67000007629395</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E124" t="n">
         <v>11.67000007629395</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E125" t="n">
         <v>11.67000007629395</v>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E126" t="n">
         <v>11.67000007629395</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E127" t="n">
         <v>11.67000007629395</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E128" t="n">
         <v>11.67000007629395</v>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E129" t="n">
         <v>11.67000007629395</v>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E130" t="n">
         <v>11.67000007629395</v>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E131" t="n">
         <v>11.67000007629395</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E132" t="n">
         <v>11.67000007629395</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E133" t="n">
         <v>11.67000007629395</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E134" t="n">
         <v>11.67000007629395</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E135" t="n">
         <v>11.67000007629395</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E136" t="n">
         <v>11.67000007629395</v>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E137" t="n">
         <v>11.67000007629395</v>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E138" t="n">
         <v>11.67000007629395</v>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E139" t="n">
         <v>11.67000007629395</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E140" t="n">
         <v>11.67000007629395</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E141" t="n">
         <v>11.67000007629395</v>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E142" t="n">
         <v>11.67000007629395</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E143" t="n">
         <v>11.67000007629395</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E144" t="n">
         <v>11.67000007629395</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E145" t="n">
         <v>11.67000007629395</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E146" t="n">
         <v>11.67000007629395</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E147" t="n">
         <v>11.67000007629395</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E148" t="n">
         <v>11.67000007629395</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E149" t="n">
         <v>11.67000007629395</v>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E150" t="n">
         <v>11.67000007629395</v>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E151" t="n">
         <v>11.67000007629395</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E152" t="n">
         <v>11.67000007629395</v>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E153" t="n">
         <v>11.67000007629395</v>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E154" t="n">
         <v>11.67000007629395</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E155" t="n">
         <v>11.67000007629395</v>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E156" t="n">
         <v>11.67000007629395</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E157" t="n">
         <v>11.67000007629395</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E158" t="n">
         <v>11.67000007629395</v>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E159" t="n">
         <v>11.67000007629395</v>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E160" t="n">
         <v>11.67000007629395</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E161" t="n">
         <v>11.67000007629395</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E162" t="n">
         <v>11.67000007629395</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E163" t="n">
         <v>11.67000007629395</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E164" t="n">
         <v>11.67000007629395</v>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E165" t="n">
         <v>11.67000007629395</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E166" t="n">
         <v>11.67000007629395</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E167" t="n">
         <v>11.67000007629395</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E168" t="n">
         <v>11.67000007629395</v>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E169" t="n">
         <v>11.67000007629395</v>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>11.36270046234131</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="E170" t="n">
         <v>11.67000007629395</v>
